--- a/Controle Financeiro Geral.xlsx
+++ b/Controle Financeiro Geral.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,51 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PIX Cora</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2640.6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>50271593000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>50271593000107</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>07 at 11.56.00 AM_1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
         </is>
       </c>
     </row>
